--- a/output/pdf_financials_xlsx/FIH.U.xlsx
+++ b/output/pdf_financials_xlsx/FIH.U.xlsx
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>44.699</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>54.343</v>
+        <v>9.644</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>106.944</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>54.343</v>
+        <v>9.644</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>106.944</v>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -20671,7 +20671,11 @@
           <t>General and administration expenses 14</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -20726,7 +20730,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -22639,7 +22643,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -23004,7 +23008,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E253" s="5" t="n">
         <v>5.515</v>
       </c>

--- a/output/pdf_financials_xlsx/FIH.U.xlsx
+++ b/output/pdf_financials_xlsx/FIH.U.xlsx
@@ -557,15 +557,11 @@
       <c r="J4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -645,15 +641,11 @@
       <c r="J6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -859,15 +851,11 @@
       <c r="J11" s="3" t="n">
         <v>-146960</v>
       </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K11" s="3" t="n">
+        <v>-73840</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-79284</v>
       </c>
     </row>
     <row r="12">
@@ -1279,7 +1267,7 @@
         <v>0.191488</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.383846</v>
+        <v>383846</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-32737</v>
@@ -1405,7 +1393,7 @@
         <v>0.191488</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.383846</v>
+        <v>383846</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-32737</v>
@@ -6125,7 +6113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O257"/>
+  <dimension ref="A1:O271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20259,147 +20247,183 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Interest 6</t>
+          <t>Issuance of 1 Multiple Voting Share.................................................................................................</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F211" s="5" t="n">
-        <v>44.699</v>
-      </c>
-      <c r="G211" s="5" t="n">
-        <v>21.343</v>
-      </c>
-      <c r="H211" s="5" t="n">
-        <v>0.021848</v>
-      </c>
-      <c r="I211" s="5" t="n">
-        <v>0.021659</v>
-      </c>
-      <c r="J211" s="5" t="n">
-        <v>0.004859</v>
-      </c>
-      <c r="K211" s="5" t="n">
-        <v>0.0055</v>
-      </c>
-      <c r="L211" s="5" t="n">
-        <v>0.011353</v>
-      </c>
-      <c r="M211" s="5" t="n">
-        <v>16833</v>
-      </c>
-      <c r="N211" s="5" t="n">
-        <v>19504</v>
-      </c>
-      <c r="O211" s="5" t="n">
-        <v>7545</v>
+      <c r="E211" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Dividends 6</t>
+          <t>Due to related party...........................................................................................................................</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E212" s="5" t="n">
+        <v>0.244722</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G212" s="5" t="n">
-        <v>5.611</v>
-      </c>
-      <c r="H212" s="5" t="n">
-        <v>0.008626999999999999</v>
-      </c>
-      <c r="I212" s="5" t="n">
-        <v>0.008699</v>
-      </c>
-      <c r="J212" s="5" t="n">
-        <v>0.010141</v>
-      </c>
-      <c r="K212" s="5" t="n">
-        <v>0.027468</v>
-      </c>
-      <c r="L212" s="5" t="n">
-        <v>0.023985</v>
-      </c>
-      <c r="M212" s="5" t="n">
-        <v>28831</v>
-      </c>
-      <c r="N212" s="5" t="n">
-        <v>41946</v>
-      </c>
-      <c r="O212" s="5" t="n">
-        <v>48185</v>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Net realized gains on investments 6</t>
+          <t>Increase in cash ...............................................................................................................................</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NetRealizedGainLossOnInvestments</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="n">
+        <v>0.244732</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G213" s="5" t="n">
-        <v>3.392</v>
-      </c>
-      <c r="H213" s="5" t="n">
-        <v>1.195</v>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -20411,39 +20435,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K213" s="5" t="n">
-        <v>0.227193</v>
-      </c>
-      <c r="L213" s="5" t="n">
-        <v>0.095882</v>
-      </c>
-      <c r="M213" s="5" t="n">
-        <v>193203</v>
-      </c>
-      <c r="N213" s="5" t="n">
-        <v>218871</v>
-      </c>
-      <c r="O213" s="5" t="n">
-        <v>53493</v>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Net change in unrealized gains (losses) on investments 6</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
+          <t>Cash, beginning of period.................................................................................................................</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -20484,69 +20522,95 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M214" s="5" t="n">
-        <v>361702</v>
-      </c>
-      <c r="N214" s="5" t="n">
-        <v>-167654</v>
-      </c>
-      <c r="O214" s="5" t="n">
-        <v>527593</v>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Financing activity</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Net foreign exchange losses 6</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period .........................................................................................................................</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="n">
+        <v>0.244732</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G215" s="5" t="n">
-        <v>-6.737</v>
-      </c>
-      <c r="H215" s="5" t="n">
-        <v>-0.014277</v>
-      </c>
-      <c r="I215" s="5" t="n">
-        <v>-0.034853</v>
-      </c>
-      <c r="J215" s="5" t="n">
-        <v>-0.013806</v>
-      </c>
-      <c r="K215" s="5" t="n">
-        <v>-0.005557</v>
-      </c>
-      <c r="L215" s="5" t="n">
-        <v>-0.04735</v>
-      </c>
-      <c r="M215" s="5" t="n">
-        <v>-1713</v>
-      </c>
-      <c r="N215" s="5" t="n">
-        <v>-12616</v>
-      </c>
-      <c r="O215" s="5" t="n">
-        <v>-27963</v>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -20562,7 +20626,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Income total</t>
+          <t>Interest 6</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -20572,34 +20636,34 @@
         </is>
       </c>
       <c r="F216" s="5" t="n">
-        <v>65.251</v>
+        <v>44.699</v>
       </c>
       <c r="G216" s="5" t="n">
-        <v>128.604</v>
+        <v>21.343</v>
       </c>
       <c r="H216" s="5" t="n">
-        <v>0.60967</v>
+        <v>0.021848</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>0.166518</v>
+        <v>0.021659</v>
       </c>
       <c r="J216" s="5" t="n">
-        <v>0.712689</v>
+        <v>0.004859</v>
       </c>
       <c r="K216" s="5" t="n">
-        <v>0.693539</v>
+        <v>0.0055</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>0.237526</v>
+        <v>0.011353</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>598856</v>
+        <v>16833</v>
       </c>
       <c r="N216" s="5" t="n">
-        <v>100051</v>
+        <v>19504</v>
       </c>
       <c r="O216" s="5" t="n">
-        <v>608853</v>
+        <v>7545</v>
       </c>
     </row>
     <row r="217">
@@ -20610,12 +20674,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Investment and advisory fees 12</t>
+          <t>Dividends 6</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -20624,35 +20688,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F217" s="5" t="n">
-        <v>5.393</v>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>12.552</v>
+        <v>5.611</v>
       </c>
       <c r="H217" s="5" t="n">
-        <v>0.027531</v>
+        <v>0.008626999999999999</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>0.033908</v>
+        <v>0.008699</v>
       </c>
       <c r="J217" s="5" t="n">
-        <v>0.027473</v>
+        <v>0.010141</v>
       </c>
       <c r="K217" s="5" t="n">
-        <v>0.040775</v>
+        <v>0.027468</v>
       </c>
       <c r="L217" s="5" t="n">
-        <v>0.038988</v>
+        <v>0.023985</v>
       </c>
       <c r="M217" s="5" t="n">
-        <v>39382</v>
+        <v>28831</v>
       </c>
       <c r="N217" s="5" t="n">
-        <v>40405</v>
+        <v>41946</v>
       </c>
       <c r="O217" s="5" t="n">
-        <v>42155</v>
+        <v>48185</v>
       </c>
     </row>
     <row r="218">
@@ -20663,17 +20729,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>General and administration expenses 14</t>
+          <t>Net realized gains on investments 6</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>NetRealizedGainLossOnInvestments</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -20681,35 +20747,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F218" s="5" t="n">
-        <v>5.515</v>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>4.937</v>
+        <v>3.392</v>
       </c>
       <c r="H218" s="5" t="n">
-        <v>0.004166</v>
-      </c>
-      <c r="I218" s="5" t="n">
-        <v>0.004079</v>
-      </c>
-      <c r="J218" s="5" t="n">
-        <v>0.0053</v>
+        <v>1.195</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K218" s="5" t="n">
-        <v>0.005526</v>
+        <v>0.227193</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>0.01347</v>
+        <v>0.095882</v>
       </c>
       <c r="M218" s="5" t="n">
-        <v>12672</v>
+        <v>193203</v>
       </c>
       <c r="N218" s="5" t="n">
-        <v>7914</v>
+        <v>218871</v>
       </c>
       <c r="O218" s="5" t="n">
-        <v>7757</v>
+        <v>53493</v>
       </c>
     </row>
     <row r="219">
@@ -20720,19 +20792,15 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Interest expense 7</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Net change in unrealized gains (losses) on investments 6</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -20743,32 +20811,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G219" s="5" t="n">
-        <v>4.171</v>
-      </c>
-      <c r="H219" s="5" t="n">
-        <v>0.015664</v>
-      </c>
-      <c r="I219" s="5" t="n">
-        <v>0.028898</v>
-      </c>
-      <c r="J219" s="5" t="n">
-        <v>0.038781</v>
-      </c>
-      <c r="K219" s="5" t="n">
-        <v>0.028515</v>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v>0.025521</v>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M219" s="5" t="n">
-        <v>25521</v>
+        <v>361702</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>25521</v>
+        <v>-167654</v>
       </c>
       <c r="O219" s="5" t="n">
-        <v>29372</v>
+        <v>527593</v>
       </c>
     </row>
     <row r="220">
@@ -20779,53 +20859,51 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Net foreign exchange losses 6</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F220" s="5" t="n">
-        <v>10.908</v>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>21.66</v>
+        <v>-6.737</v>
       </c>
       <c r="H220" s="5" t="n">
-        <v>0.159579</v>
+        <v>-0.014277</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>0.066885</v>
+        <v>-0.034853</v>
       </c>
       <c r="J220" s="5" t="n">
-        <v>0.120068</v>
+        <v>-0.013806</v>
       </c>
       <c r="K220" s="5" t="n">
-        <v>0.160009</v>
+        <v>-0.005557</v>
       </c>
       <c r="L220" s="5" t="n">
-        <v>0.041551</v>
+        <v>-0.04735</v>
       </c>
       <c r="M220" s="5" t="n">
-        <v>146960</v>
+        <v>-1713</v>
       </c>
       <c r="N220" s="5" t="n">
-        <v>73840</v>
+        <v>-12616</v>
       </c>
       <c r="O220" s="5" t="n">
-        <v>79284</v>
+        <v>-27963</v>
       </c>
     </row>
     <row r="221">
@@ -20836,53 +20914,49 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Earnings before income taxes</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Income total</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F221" s="5" t="n">
-        <v>54.343</v>
+        <v>65.251</v>
       </c>
       <c r="G221" s="5" t="n">
-        <v>106.944</v>
+        <v>128.604</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>0.450091</v>
+        <v>0.60967</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>0.099633</v>
+        <v>0.166518</v>
       </c>
       <c r="J221" s="5" t="n">
-        <v>0.592621</v>
+        <v>0.712689</v>
       </c>
       <c r="K221" s="5" t="n">
-        <v>0.5335299999999999</v>
+        <v>0.693539</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>0.195975</v>
+        <v>0.237526</v>
       </c>
       <c r="M221" s="5" t="n">
-        <v>451896</v>
+        <v>598856</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>26211</v>
+        <v>100051</v>
       </c>
       <c r="O221" s="5" t="n">
-        <v>529569</v>
+        <v>608853</v>
       </c>
     </row>
     <row r="222">
@@ -20898,54 +20972,44 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Provision for income taxes 10</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Investment and advisory fees 12</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F222" s="5" t="n">
+        <v>5.393</v>
+      </c>
+      <c r="G222" s="5" t="n">
+        <v>12.552</v>
+      </c>
+      <c r="H222" s="5" t="n">
+        <v>0.027531</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>0.003201</v>
+        <v>0.033908</v>
       </c>
       <c r="J222" s="5" t="n">
-        <v>0.076283</v>
+        <v>0.027473</v>
       </c>
       <c r="K222" s="5" t="n">
-        <v>0.03903</v>
+        <v>0.040775</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>0.004487</v>
+        <v>0.038988</v>
       </c>
       <c r="M222" s="5" t="n">
-        <v>68050</v>
+        <v>39382</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>58948</v>
+        <v>40405</v>
       </c>
       <c r="O222" s="5" t="n">
-        <v>87477</v>
+        <v>42155</v>
       </c>
     </row>
     <row r="223">
@@ -20961,58 +21025,48 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Net earnings (loss)</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
+          <t>General and administration expenses 14</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F223" s="5" t="n">
+        <v>5.515</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>4.937</v>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>0.004166</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>0.004079</v>
+      </c>
+      <c r="J223" s="5" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>0.005526</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>0.01347</v>
       </c>
       <c r="M223" s="5" t="n">
-        <v>383846</v>
+        <v>12672</v>
       </c>
       <c r="N223" s="5" t="n">
-        <v>-32737</v>
+        <v>7914</v>
       </c>
       <c r="O223" s="5" t="n">
-        <v>442092</v>
+        <v>7757</v>
       </c>
     </row>
     <row r="224">
@@ -21023,15 +21077,19 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Shareholders of Fairfax India</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Interest expense 7</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -21042,40 +21100,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G224" s="5" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>0.015664</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>0.028898</v>
+      </c>
+      <c r="J224" s="5" t="n">
+        <v>0.038781</v>
       </c>
       <c r="K224" s="5" t="n">
-        <v>0.494514</v>
+        <v>0.028515</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>0.191439</v>
+        <v>0.025521</v>
       </c>
       <c r="M224" s="5" t="n">
-        <v>371770</v>
+        <v>25521</v>
       </c>
       <c r="N224" s="5" t="n">
-        <v>-41173</v>
+        <v>25521</v>
       </c>
       <c r="O224" s="5" t="n">
-        <v>410526</v>
+        <v>29372</v>
       </c>
     </row>
     <row r="225">
@@ -21086,17 +21136,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Non-controlling interests 8</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -21104,49 +21154,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F225" s="5" t="n">
+        <v>10.908</v>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="H225" s="5" t="n">
+        <v>0.159579</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>0.066885</v>
+      </c>
+      <c r="J225" s="5" t="n">
+        <v>0.120068</v>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>0.160009</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>0.041551</v>
       </c>
       <c r="M225" s="5" t="n">
-        <v>-12076</v>
+        <v>146960</v>
       </c>
       <c r="N225" s="5" t="n">
-        <v>-8436</v>
+        <v>73840</v>
       </c>
       <c r="O225" s="5" t="n">
-        <v>-31566</v>
+        <v>79284</v>
       </c>
     </row>
     <row r="226">
@@ -21157,59 +21193,53 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Attributable to total</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>Earnings before income taxes</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F226" s="5" t="n">
+        <v>54.343</v>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>106.944</v>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>0.450091</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>0.099633</v>
+      </c>
+      <c r="J226" s="5" t="n">
+        <v>0.592621</v>
       </c>
       <c r="K226" s="5" t="n">
-        <v>0.4945</v>
+        <v>0.5335299999999999</v>
       </c>
       <c r="L226" s="5" t="n">
-        <v>0.191488</v>
+        <v>0.195975</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>383846</v>
+        <v>451896</v>
       </c>
       <c r="N226" s="5" t="n">
-        <v>-32737</v>
+        <v>26211</v>
       </c>
       <c r="O226" s="5" t="n">
-        <v>442092</v>
+        <v>529569</v>
       </c>
     </row>
     <row r="227">
@@ -21220,15 +21250,19 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Net earnings (loss) per basic and diluted share 9 $</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>Provision for income taxes 10</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -21249,34 +21283,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I227" s="5" t="n">
+        <v>0.003201</v>
+      </c>
+      <c r="J227" s="5" t="n">
+        <v>0.076283</v>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>0.03903</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>0.004487</v>
       </c>
       <c r="M227" s="5" t="n">
-        <v>2.72</v>
+        <v>68050</v>
       </c>
       <c r="N227" s="5" t="n">
-        <v>-0.3</v>
+        <v>58948</v>
       </c>
       <c r="O227" s="5" t="n">
-        <v>3.05</v>
+        <v>87477</v>
       </c>
     </row>
     <row r="228">
@@ -21287,15 +21313,19 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Shares outstanding (weighted average) 9</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Net earnings (loss)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -21326,20 +21356,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K228" s="5" t="n">
-        <v>146.379346</v>
-      </c>
-      <c r="L228" s="5" t="n">
-        <v>139.066682</v>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M228" s="5" t="n">
-        <v>136818139</v>
+        <v>383846</v>
       </c>
       <c r="N228" s="5" t="n">
-        <v>135165840</v>
+        <v>-32737</v>
       </c>
       <c r="O228" s="5" t="n">
-        <v>134792916</v>
+        <v>442092</v>
       </c>
     </row>
     <row r="229">
@@ -21350,12 +21384,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Performance fee 12</t>
+          <t>Shareholders of Fairfax India</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -21374,39 +21408,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H229" s="5" t="n">
-        <v>0.112218</v>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J229" s="5" t="n">
-        <v>0.048514</v>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>0.494514</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>0.191439</v>
       </c>
       <c r="M229" s="5" t="n">
-        <v>69385</v>
-      </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>371770</v>
+      </c>
+      <c r="N229" s="5" t="n">
+        <v>-41173</v>
+      </c>
+      <c r="O229" s="5" t="n">
+        <v>410526</v>
       </c>
     </row>
     <row r="230">
@@ -21417,15 +21447,19 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Net change in unrealized gains on investments 6</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Non-controlling interests 8</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -21446,30 +21480,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I230" s="5" t="n">
-        <v>0.178998</v>
-      </c>
-      <c r="J230" s="5" t="n">
-        <v>0.530372</v>
-      </c>
-      <c r="K230" s="5" t="n">
-        <v>0.438935</v>
-      </c>
-      <c r="L230" s="5" t="n">
-        <v>0.153656</v>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M230" s="5" t="n">
-        <v>0.361702</v>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-12076</v>
+      </c>
+      <c r="N230" s="5" t="n">
+        <v>-8436</v>
+      </c>
+      <c r="O230" s="5" t="n">
+        <v>-31566</v>
       </c>
     </row>
     <row r="231">
@@ -21480,12 +21518,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Performance fee (recovery) 12</t>
+          <t>Attributable to total</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -21520,23 +21558,19 @@
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>0.085193</v>
+        <v>0.4945</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>-0.036428</v>
+        <v>0.191488</v>
       </c>
       <c r="M231" s="5" t="n">
-        <v>0.069385</v>
-      </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>383846</v>
+      </c>
+      <c r="N231" s="5" t="n">
+        <v>-32737</v>
+      </c>
+      <c r="O231" s="5" t="n">
+        <v>442092</v>
       </c>
     </row>
     <row r="232">
@@ -21547,57 +21581,63 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Net earnings</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Net earnings (loss) per basic and diluted share 9 $</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F232" s="5" t="n">
-        <v>40.939</v>
-      </c>
-      <c r="G232" s="5" t="n">
-        <v>107.825</v>
-      </c>
-      <c r="H232" s="5" t="n">
-        <v>0.452509</v>
-      </c>
-      <c r="I232" s="5" t="n">
-        <v>0.096432</v>
-      </c>
-      <c r="J232" s="5" t="n">
-        <v>0.516338</v>
-      </c>
-      <c r="K232" s="5" t="n">
-        <v>0.4945</v>
-      </c>
-      <c r="L232" s="5" t="n">
-        <v>0.191488</v>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M232" s="5" t="n">
-        <v>0.383846</v>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.72</v>
+      </c>
+      <c r="N232" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="O232" s="5" t="n">
+        <v>3.05</v>
       </c>
     </row>
     <row r="233">
@@ -21613,14 +21653,10 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Shares outstanding (weighted average) 9</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -21652,23 +21688,19 @@
         </is>
       </c>
       <c r="K233" s="5" t="n">
-        <v>1.4e-05</v>
+        <v>146.379346</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>-4.9e-05</v>
+        <v>139.066682</v>
       </c>
       <c r="M233" s="5" t="n">
-        <v>-0.012076</v>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>136818139</v>
+      </c>
+      <c r="N233" s="5" t="n">
+        <v>135165840</v>
+      </c>
+      <c r="O233" s="5" t="n">
+        <v>134792916</v>
       </c>
     </row>
     <row r="234">
@@ -21679,12 +21711,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Net earnings per share 9 $</t>
+          <t>Performance fee 12</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -21703,29 +21735,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H234" s="5" t="n">
+        <v>0.112218</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K234" s="5" t="n">
-        <v>3.38e-06</v>
-      </c>
-      <c r="L234" s="5" t="n">
-        <v>1.38e-06</v>
+      <c r="J234" s="5" t="n">
+        <v>0.048514</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M234" s="5" t="n">
-        <v>2.72e-06</v>
+        <v>69385</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -21746,12 +21778,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Net earnings per diluted share 9 $</t>
+          <t>Net change in unrealized gains on investments 6</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -21775,24 +21807,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I235" s="5" t="n">
+        <v>0.178998</v>
+      </c>
+      <c r="J235" s="5" t="n">
+        <v>0.530372</v>
       </c>
       <c r="K235" s="5" t="n">
-        <v>3.22e-06</v>
+        <v>0.438935</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>1.34e-06</v>
+        <v>0.153656</v>
       </c>
       <c r="M235" s="5" t="n">
-        <v>2.72e-06</v>
+        <v>0.361702</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -21813,53 +21841,53 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Net realized gains (losses) on investments 6</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>NetRealizedGainLossOnInvestments</t>
-        </is>
-      </c>
+          <t>Performance fee (recovery) 12</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F236" s="5" t="n">
-        <v>-0.209</v>
-      </c>
-      <c r="G236" s="5" t="n">
-        <v>3.392</v>
-      </c>
-      <c r="H236" s="5" t="n">
-        <v>0.001195</v>
-      </c>
-      <c r="I236" s="5" t="n">
-        <v>-0.007985000000000001</v>
-      </c>
-      <c r="J236" s="5" t="n">
-        <v>0.181123</v>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>0.085193</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>-0.036428</v>
+      </c>
+      <c r="M236" s="5" t="n">
+        <v>0.069385</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -21885,46 +21913,42 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Net earnings per share 9 $</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Net earnings</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F237" s="5" t="n">
+        <v>40.939</v>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1.01e-06</v>
+        <v>107.825</v>
       </c>
       <c r="H237" s="5" t="n">
-        <v>3.1e-06</v>
+        <v>0.452509</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>6.3e-07</v>
+        <v>0.096432</v>
       </c>
       <c r="J237" s="5" t="n">
-        <v>3.38e-06</v>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.516338</v>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>0.191488</v>
+      </c>
+      <c r="M237" s="5" t="n">
+        <v>0.383846</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
@@ -21945,15 +21969,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Net earnings per diluted share 9 $</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -21964,32 +21992,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G238" s="5" t="n">
-        <v>0.00101</v>
-      </c>
-      <c r="H238" s="5" t="n">
-        <v>2.94e-06</v>
-      </c>
-      <c r="I238" s="5" t="n">
-        <v>6.3e-07</v>
-      </c>
-      <c r="J238" s="5" t="n">
-        <v>3.3e-06</v>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>1.4e-05</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>-4.9e-05</v>
+      </c>
+      <c r="M238" s="5" t="n">
+        <v>-0.012076</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -22010,12 +22040,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Shares outstanding (weighted average) 9</t>
+          <t>Net earnings per share 9 $</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -22029,32 +22059,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G239" s="5" t="n">
-        <v>106517.213</v>
-      </c>
-      <c r="H239" s="5" t="n">
-        <v>146.03547</v>
-      </c>
-      <c r="I239" s="5" t="n">
-        <v>153.108655</v>
-      </c>
-      <c r="J239" s="5" t="n">
-        <v>152.654875</v>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>3.38e-06</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>1.38e-06</v>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>2.72e-06</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -22075,12 +22107,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Net change in unrealized gains on investments and other costs 6</t>
+          <t>Net earnings per diluted share 9 $</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -22094,34 +22126,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G240" s="5" t="n">
-        <v>104.995</v>
-      </c>
-      <c r="H240" s="5" t="n">
-        <v>0.5922770000000001</v>
-      </c>
-      <c r="I240" s="5" t="n">
-        <v>0.178998</v>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K240" s="5" t="n">
+        <v>3.22e-06</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>1.34e-06</v>
+      </c>
+      <c r="M240" s="5" t="n">
+        <v>2.72e-06</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -22142,17 +22174,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Provision for (recovery of) income taxes 10</t>
+          <t>Net realized gains (losses) on investments 6</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>NetRealizedGainLossOnInvestments</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -22161,21 +22193,19 @@
         </is>
       </c>
       <c r="F241" s="5" t="n">
-        <v>13.404</v>
+        <v>-0.209</v>
       </c>
       <c r="G241" s="5" t="n">
-        <v>-0.881</v>
+        <v>3.392</v>
       </c>
       <c r="H241" s="5" t="n">
-        <v>-0.002418</v>
+        <v>0.001195</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>0.003201</v>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.007985000000000001</v>
+      </c>
+      <c r="J241" s="5" t="n">
+        <v>0.181123</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -22216,14 +22246,10 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Recovery of income taxes 10</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Net earnings per share 9 $</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -22235,20 +22261,16 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>-0.881</v>
+        <v>1.01e-06</v>
       </c>
       <c r="H242" s="5" t="n">
-        <v>-2.418</v>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.1e-06</v>
+      </c>
+      <c r="I242" s="5" t="n">
+        <v>6.3e-07</v>
+      </c>
+      <c r="J242" s="5" t="n">
+        <v>3.38e-06</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -22284,44 +22306,36 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Net unrealized gains on investments 6</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>NetRealizedGainLossOnInvestments</t>
-        </is>
-      </c>
+          <t>Net earnings per diluted share 9 $</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F243" s="5" t="n">
-        <v>14.19</v>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>104.995</v>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00101</v>
+      </c>
+      <c r="H243" s="5" t="n">
+        <v>2.94e-06</v>
+      </c>
+      <c r="I243" s="5" t="n">
+        <v>6.3e-07</v>
+      </c>
+      <c r="J243" s="5" t="n">
+        <v>3.3e-06</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -22357,12 +22371,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Net foreign exchange gains (losses) 6</t>
+          <t>Shares outstanding (weighted average) 9</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -22371,26 +22385,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F244" s="5" t="n">
-        <v>6.571</v>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>-6.737</v>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>106517.213</v>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>146.03547</v>
+      </c>
+      <c r="I244" s="5" t="n">
+        <v>153.108655</v>
+      </c>
+      <c r="J244" s="5" t="n">
+        <v>152.654875</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -22426,39 +22436,33 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Net earnings per share (basic and diluted) 9 $</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Net change in unrealized gains on investments and other costs 6</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F245" s="5" t="n">
-        <v>4.2e-07</v>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>1.01e-06</v>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>104.995</v>
+      </c>
+      <c r="H245" s="5" t="n">
+        <v>0.5922770000000001</v>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>0.178998</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -22504,30 +22508,30 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Shares outstanding (weighted average – basic and diluted) 9</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>Provision for (recovery of) income taxes 10</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F246" s="5" t="n">
-        <v>98019.189</v>
+        <v>13.404</v>
       </c>
       <c r="G246" s="5" t="n">
-        <v>106517.213</v>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.881</v>
+      </c>
+      <c r="H246" s="5" t="n">
+        <v>-0.002418</v>
+      </c>
+      <c r="I246" s="5" t="n">
+        <v>0.003201</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -22566,28 +22570,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" s="5" t="n">
-        <v>2.014</v>
-      </c>
-      <c r="F247" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Recovery of income taxes 10</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G247" s="5" t="n">
+        <v>-0.881</v>
+      </c>
+      <c r="H247" s="5" t="n">
+        <v>-2.418</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -22638,12 +22650,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Net unrealized gains on investments 6</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>NetRealizedGainLossOnInvestments</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -22652,12 +22664,10 @@
         </is>
       </c>
       <c r="F248" s="5" t="n">
-        <v>44.699</v>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.19</v>
+      </c>
+      <c r="G248" s="5" t="n">
+        <v>104.995</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -22713,26 +22723,20 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Net realized gains on investments</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>NetRealizedGainLossOnInvestments</t>
-        </is>
-      </c>
+          <t>Net foreign exchange gains (losses) 6</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F249" s="5" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.571</v>
+      </c>
+      <c r="G249" s="5" t="n">
+        <v>-6.737</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -22783,17 +22787,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Net unrealized gains on investments</t>
+          <t>Net earnings per share (basic and diluted) 9 $</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NetRealizedGainLossOnInvestments</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -22802,12 +22806,10 @@
         </is>
       </c>
       <c r="F250" s="5" t="n">
-        <v>17.675</v>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.2e-07</v>
+      </c>
+      <c r="G250" s="5" t="n">
+        <v>1.01e-06</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -22858,12 +22860,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Net foreign exchange gains</t>
+          <t>Shares outstanding (weighted average – basic and diluted) 9</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -22873,12 +22875,10 @@
         </is>
       </c>
       <c r="F251" s="5" t="n">
-        <v>2.794</v>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>98019.189</v>
+      </c>
+      <c r="G251" s="5" t="n">
+        <v>106517.213</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -22927,24 +22927,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Investment and advisory fees 11</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E252" s="5" t="n">
+        <v>2.014</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>5.393</v>
+        <v>0.031</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -23000,24 +22994,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E253" s="5" t="n">
-        <v>5.515</v>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F253" s="5" t="n">
-        <v>0.013</v>
+        <v>44.699</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -23073,17 +23069,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Provision for income taxes 9</t>
+          <t>Net realized gains on investments</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>NetRealizedGainLossOnInvestments</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -23092,7 +23088,7 @@
         </is>
       </c>
       <c r="F254" s="5" t="n">
-        <v>13.404</v>
+        <v>0.083</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -23148,22 +23144,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Net earnings attributable to common shareholders</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>Net unrealized gains on investments</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NetRealizedGainLossOnInvestments</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F255" s="5" t="n">
-        <v>40.939</v>
+        <v>17.675</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -23219,12 +23219,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Net earnings per share 8 $</t>
+          <t>Net foreign exchange gains</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -23234,7 +23234,7 @@
         </is>
       </c>
       <c r="F256" s="5" t="n">
-        <v>4.2e-07</v>
+        <v>2.794</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -23295,57 +23295,1035 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
+          <t>Investment and advisory fees 11</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>5.393</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>General and administration expenses</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>5.515</v>
+      </c>
+      <c r="F258" s="5" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Provision for income taxes 9</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F259" s="5" t="n">
+        <v>13.404</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Net earnings attributable to common shareholders</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="n">
+        <v>40.939</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Net earnings per share 8 $</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="n">
+        <v>4.2e-07</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
           <t>Shares outstanding (weighted average) 8</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" s="5" t="n">
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="F257" s="5" t="n">
+      <c r="F262" s="5" t="n">
         <v>98019.189</v>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O257" t="inlineStr">
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Revenue...................................................................................................................................................</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Expenses..................................................................................................................................................</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Provision for income taxes.......................................................................................................................</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Net earnings............................................................................................................................................</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Other comprehensive income, net of income taxes .............................................................................</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Comprehensive income..........................................................................................................................</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Shareholder’s Equity, beginning of period..........................................................................................</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Issuance of 1 Multiple Voting Share........................................................................................................</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Shareholder’s Equity, end of period ....................................................................................................</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
         <is>
           <t>-</t>
         </is>
